--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484637_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484637_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4798</v>
+        <v>3.0456</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1652</v>
+        <v>1.7806</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3146</v>
+        <v>1.2651</v>
       </c>
       <c r="G2" t="n">
         <v>1.2646</v>
@@ -610,13 +610,13 @@
         <v>0.9163</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9195</v>
+        <v>0.4853</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0068</v>
+        <v>0.6222</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0873</v>
+        <v>-0.1369</v>
       </c>
       <c r="V2" t="n">
         <v>2.212</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5972</v>
+        <v>2.1907</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3525</v>
+        <v>2.8717</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7553</v>
+        <v>-0.681</v>
       </c>
       <c r="G3" t="n">
         <v>1.2925</v>
@@ -688,13 +688,13 @@
         <v>0.9163</v>
       </c>
       <c r="S3" t="n">
-        <v>0.214</v>
+        <v>-0.1925</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0068</v>
+        <v>0.526</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.7185</v>
       </c>
       <c r="V3" t="n">
         <v>0.1744</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6561</v>
+        <v>1.993</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8072</v>
+        <v>0.8855</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1512</v>
+        <v>1.1074</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2706</v>
+        <v>0.1351</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9345</v>
+        <v>-0.0959</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6639</v>
+        <v>0.2309</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1625</v>
+        <v>0.2833</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1208</v>
+        <v>0.7895</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0417</v>
+        <v>-0.5062</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8919</v>
+        <v>-0.1483</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1863</v>
+        <v>-0.8854</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7056</v>
+        <v>0.7371</v>
       </c>
       <c r="P4" t="n">
+        <v>1.8326</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-1.8326</v>
-      </c>
       <c r="R4" t="n">
-        <v>0.9163</v>
+        <v>2.7489</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1605</v>
+        <v>-1.5532</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1116</v>
+        <v>-0.382</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0489</v>
+        <v>-1.1712</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4622</v>
+        <v>1.5785</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5889</v>
+        <v>1.9005</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.259</v>
+        <v>1.1254</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3497</v>
+        <v>1.5738</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9093</v>
+        <v>-0.4484</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1351</v>
+        <v>1.2706</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0959</v>
+        <v>1.9345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2309</v>
+        <v>-0.6639</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2833</v>
+        <v>2.1625</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7895</v>
+        <v>2.1208</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5062</v>
+        <v>0.0417</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1483</v>
+        <v>-0.8919</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8854</v>
+        <v>-0.1863</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7371</v>
+        <v>-0.7056</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7489</v>
+        <v>0.9163</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.2872</v>
+        <v>-0.6912</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.345</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3694</v>
+        <v>-0.3462</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5785</v>
+        <v>1.4622</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9005</v>
+        <v>1.5889</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3574</v>
+        <v>0.1433</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5455</v>
+        <v>-0.8339</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9029</v>
+        <v>0.9772</v>
       </c>
       <c r="G6" t="n">
         <v>-2.0293</v>
@@ -922,13 +922,13 @@
         <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7087</v>
+        <v>0.4945</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8416</v>
+        <v>0.5532</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.133</v>
+        <v>-0.0586</v>
       </c>
       <c r="V6" t="n">
         <v>0.945</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9153</v>
+        <v>-0.253</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2054</v>
+        <v>-0.5184</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2902</v>
+        <v>0.2654</v>
       </c>
       <c r="G7" t="n">
         <v>2.4843</v>
@@ -1000,13 +1000,13 @@
         <v>3.1154</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0504</v>
+        <v>-1.3882</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2481</v>
+        <v>-0.5611</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8024</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-1.7156</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.354</v>
+        <v>-2.3019</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0738</v>
+        <v>-1.9226</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2803</v>
+        <v>-0.3793</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1153</v>
@@ -1078,13 +1078,13 @@
         <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2388</v>
+        <v>-1.1866</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6056</v>
+        <v>-0.4544</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6332</v>
+        <v>-0.7323</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0611</v>
+        <v>-3.8108</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1052</v>
+        <v>-1.954</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9559</v>
+        <v>-1.8568</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7683</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8035</v>
+        <v>-1.5532</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7157</v>
+        <v>-0.5645</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0878</v>
+        <v>-0.9887</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1572</v>
+        <v>-4.3531</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0961</v>
+        <v>-4.0028</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0611</v>
+        <v>-0.3503</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4411</v>
+        <v>-2.524</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7041</v>
+        <v>-1.6358</v>
       </c>
       <c r="I10" t="n">
-        <v>1.263</v>
+        <v>-0.8882</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7476</v>
+        <v>-2.0397</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.0751</v>
+        <v>-0.7993</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3275</v>
+        <v>-1.2404</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6935</v>
+        <v>-0.4843</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.629</v>
+        <v>-0.8365</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0646</v>
+        <v>0.3522</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1991</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4204</v>
+        <v>-1.2234</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8092</v>
+        <v>-0.7353</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6113</v>
+        <v>-0.4881</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5785</v>
+        <v>-1.7052</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6231</v>
+        <v>-0.3115</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9554</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3711</v>
+        <v>-4.3633</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1704</v>
+        <v>-4.1783</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2008</v>
+        <v>-0.185</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5361</v>
+        <v>-2.4411</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2794</v>
+        <v>-3.7041</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2567</v>
+        <v>1.263</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0534</v>
+        <v>-1.7476</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0534</v>
+        <v>-3.0751</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.3275</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4827</v>
+        <v>-0.6935</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2259</v>
+        <v>-0.629</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2567</v>
+        <v>-0.0646</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
         <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.431</v>
+        <v>-1.6265</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1267</v>
+        <v>-0.8914</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5577</v>
+        <v>-0.7351</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7706</v>
+        <v>-1.5785</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5889</v>
+        <v>-0.6231</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3595</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9166</v>
+        <v>-4.5357</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4424</v>
+        <v>-3.4588</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4742</v>
+        <v>-1.0769</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.524</v>
+        <v>-3.5361</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6358</v>
+        <v>-3.2794</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8882</v>
+        <v>-0.2567</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0397</v>
+        <v>-3.0534</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7993</v>
+        <v>-3.0534</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2404</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4843</v>
+        <v>-0.4827</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8365</v>
+        <v>-0.2259</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3522</v>
+        <v>-0.2567</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0158</v>
+        <v>2.1991</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7869</v>
+        <v>-0.5956</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1749</v>
+        <v>-0.1617</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.612</v>
+        <v>-0.4338</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7052</v>
+        <v>-0.7706</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3115</v>
+        <v>1.5889</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3937</v>
+        <v>-2.3595</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.8942</v>
+        <v>-7.6497</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.743</v>
+        <v>-7.3995</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1512</v>
+        <v>-0.2503</v>
       </c>
       <c r="G13" t="n">
         <v>-5.5799</v>
@@ -1468,13 +1468,13 @@
         <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.652</v>
+        <v>-0.4076</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4419</v>
+        <v>-0.0984</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2101</v>
+        <v>-0.3092</v>
       </c>
       <c r="V13" t="n">
         <v>-2.212</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.32</v>
+        <v>-18.7695</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.7072</v>
+        <v>-17.1567</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.613</v>
+        <v>-1.6129</v>
       </c>
       <c r="G14" t="n">
         <v>-12.5469</v>
@@ -1525,7 +1525,7 @@
         <v>-3.6621</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.684099999999999</v>
+        <v>-3.6841</v>
       </c>
       <c r="M14" t="n">
         <v>-5.2005</v>
@@ -1537,7 +1537,7 @@
         <v>1.4396</v>
       </c>
       <c r="P14" t="n">
-        <v>6.4139</v>
+        <v>6.413900000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.6608</v>
@@ -1546,13 +1546,13 @@
         <v>21.0746</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.988499999999998</v>
+        <v>-9.438199999999998</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.0429</v>
+        <v>-2.4924</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.9459</v>
+        <v>-6.9457</v>
       </c>
       <c r="V14" t="n">
         <v>-3.1987</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.232</v>
+        <v>5.0839</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9511</v>
+        <v>3.4421</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2809</v>
+        <v>1.6418</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9052</v>
+        <v>1.7651</v>
       </c>
       <c r="H15" t="n">
-        <v>3.466</v>
+        <v>0.2906</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4392</v>
+        <v>1.4745</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2327</v>
+        <v>1.9287</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4985</v>
+        <v>0.486</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7342</v>
+        <v>1.4427</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6726</v>
+        <v>-0.1636</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9676</v>
+        <v>-0.1955</v>
       </c>
       <c r="O15" t="n">
-        <v>0.705</v>
+        <v>0.0318</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.4819</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.681</v>
+        <v>-1.0995</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4658</v>
+        <v>2.675</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7896</v>
+        <v>1.6471</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6762</v>
+        <v>1.0279</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3428</v>
+        <v>0.6439</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6097</v>
+        <v>0.9658</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1096</v>
+        <v>3.7863</v>
       </c>
       <c r="E16" t="n">
-        <v>4.596</v>
+        <v>0.0578</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5136</v>
+        <v>3.7284</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7651</v>
+        <v>0.9264</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2906</v>
+        <v>0.5128</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4745</v>
+        <v>0.4136</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9287</v>
+        <v>-0.3219</v>
       </c>
       <c r="K16" t="n">
-        <v>0.486</v>
+        <v>-0.4151</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4427</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1636</v>
+        <v>1.2483</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1955</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0318</v>
+        <v>0.3204</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7006</v>
+        <v>1.1269</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8009</v>
+        <v>0.6625</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.4643</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6439</v>
+        <v>0.6335</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9658</v>
+        <v>0.6335</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9544</v>
+        <v>3.5118</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4229</v>
+        <v>0.6434</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3773</v>
+        <v>2.8684</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9264</v>
+        <v>4.9052</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5128</v>
+        <v>3.466</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4136</v>
+        <v>1.4392</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3219</v>
+        <v>3.2327</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4151</v>
+        <v>2.4985</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.7342</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2483</v>
+        <v>1.6726</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9676</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3204</v>
+        <v>0.705</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0995</v>
+        <v>-3.4819</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-5.681</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0158</v>
+        <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2949</v>
+        <v>1.7457</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1818</v>
+        <v>1.4819</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1132</v>
+        <v>0.2637</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6335</v>
+        <v>0.3428</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6335</v>
+        <v>1.6097</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5474</v>
+        <v>3.1432</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3302</v>
+        <v>0.439</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8776</v>
+        <v>2.7042</v>
       </c>
       <c r="G18" t="n">
         <v>0.5937</v>
@@ -1858,13 +1858,13 @@
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7471</v>
+        <v>1.3429</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.184</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9311</v>
+        <v>0.7577</v>
       </c>
       <c r="V18" t="n">
         <v>2.8559</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4309</v>
+        <v>2.3887</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07820000000000001</v>
+        <v>-0.018</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3528</v>
+        <v>2.4066</v>
       </c>
       <c r="G20" t="n">
         <v>0.6583</v>
@@ -2014,13 +2014,13 @@
         <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4716</v>
+        <v>1.4293</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6946</v>
+        <v>0.5984</v>
       </c>
       <c r="U20" t="n">
-        <v>0.777</v>
+        <v>0.8309</v>
       </c>
       <c r="V20" t="n">
         <v>0.3011</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1441</v>
+        <v>2.1843</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1341</v>
+        <v>0.8274</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2782</v>
+        <v>1.3569</v>
       </c>
       <c r="G21" t="n">
         <v>1.8802</v>
@@ -2092,13 +2092,13 @@
         <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1698</v>
+        <v>1.21</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4593</v>
+        <v>0.5023</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6291</v>
+        <v>0.7077</v>
       </c>
       <c r="V21" t="n">
         <v>0.0104</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9097</v>
+        <v>2.0826</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1321</v>
+        <v>-0.459</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0418</v>
+        <v>2.5416</v>
       </c>
       <c r="G22" t="n">
         <v>0.5888</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5954</v>
+        <v>0.5775</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3854</v>
+        <v>0.2877</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.21</v>
+        <v>0.2898</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7872</v>
+        <v>1.0189</v>
       </c>
       <c r="E23" t="n">
         <v>-1.4041</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1913</v>
+        <v>2.4229</v>
       </c>
       <c r="G23" t="n">
         <v>2.665</v>
@@ -2248,13 +2248,13 @@
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0385</v>
+        <v>0.2702</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1847</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2233</v>
+        <v>0.4549</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6335</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3536</v>
+        <v>0.7659</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3866</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7402</v>
+        <v>0.864</v>
       </c>
       <c r="G24" t="n">
         <v>-0.674</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2839</v>
+        <v>0.1284</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.129</v>
+        <v>0.1595</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.155</v>
+        <v>-0.0311</v>
       </c>
       <c r="V24" t="n">
         <v>0.945</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6227</v>
+        <v>-1.3808</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2218</v>
+        <v>0.4141</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8445</v>
+        <v>-1.795</v>
       </c>
       <c r="G25" t="n">
         <v>-0.216</v>
@@ -2404,13 +2404,13 @@
         <v>0.1833</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4617</v>
+        <v>-0.2198</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0181</v>
+        <v>0.2104</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4798</v>
+        <v>-0.4302</v>
       </c>
       <c r="V25" t="n">
         <v>-0.945</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.448</v>
+        <v>-1.8463</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1016</v>
+        <v>-2.5247</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6536</v>
+        <v>0.6784</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8417</v>
@@ -2482,13 +2482,13 @@
         <v>0.9163</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3649</v>
+        <v>0.9666</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1086</v>
+        <v>0.6855</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2563</v>
+        <v>0.2811</v>
       </c>
       <c r="V26" t="n">
         <v>0.3115</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.5786</v>
+        <v>-2.6368</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.823</v>
+        <v>-2.2076</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.4291</v>
       </c>
       <c r="G27" t="n">
         <v>-1.2047</v>
@@ -2560,13 +2560,13 @@
         <v>0.9163</v>
       </c>
       <c r="S27" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0181</v>
       </c>
       <c r="T27" t="n">
-        <v>0.6946</v>
+        <v>0.31</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6183</v>
+        <v>-0.2919</v>
       </c>
       <c r="V27" t="n">
         <v>-1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>19.3201</v>
+        <v>20.6022</v>
       </c>
       <c r="E28" t="n">
-        <v>1.613000000000001</v>
+        <v>1.612800000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>17.7073</v>
+        <v>18.9891</v>
       </c>
       <c r="G28" t="n">
         <v>12.5468</v>
@@ -2638,16 +2638,16 @@
         <v>14.6606</v>
       </c>
       <c r="S28" t="n">
-        <v>9.9885</v>
+        <v>11.2708</v>
       </c>
       <c r="T28" t="n">
         <v>6.945799999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>3.0428</v>
+        <v>4.324800000000001</v>
       </c>
       <c r="V28" t="n">
-        <v>3.198599999999999</v>
+        <v>3.1986</v>
       </c>
       <c r="W28" t="n">
         <v>10.5408</v>
